--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -4411,7 +4411,7 @@
         <v>129572938</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>129573058</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>129573170</v>
       </c>
       <c r="B37" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>129582787</v>
       </c>
       <c r="B38" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3255,12 +3255,7 @@
         <v>104882700</v>
       </c>
       <c r="B25" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,16 +3281,24 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523080.114410902</v>
+        <v>523080</v>
       </c>
       <c r="R25" t="n">
-        <v>6435750.022629176</v>
+        <v>6435750</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3325,27 +3328,18 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -4411,7 +4405,7 @@
         <v>129572938</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4522,7 +4516,7 @@
         <v>129573058</v>
       </c>
       <c r="B36" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4627,7 @@
         <v>129573170</v>
       </c>
       <c r="B37" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4744,7 +4738,7 @@
         <v>129582787</v>
       </c>
       <c r="B38" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -4405,7 +4405,7 @@
         <v>129572938</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>129573058</v>
       </c>
       <c r="B36" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>129573170</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>129582787</v>
       </c>
       <c r="B38" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -4405,7 +4405,7 @@
         <v>129572938</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>129573058</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>129573170</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>129582787</v>
       </c>
       <c r="B38" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3139,54 +3139,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104873058</v>
+        <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kinda, Ög</t>
+          <t>Trollgölen, V, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523191.6660127564</v>
+        <v>523123</v>
       </c>
       <c r="R24" t="n">
-        <v>6435709.402463616</v>
+        <v>6435810</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3208,24 +3202,19 @@
           <t>Kisa</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>E-Kin-0540</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,68 +3229,70 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Staffan Carlsson, Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104882700</v>
+        <v>104873058</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>90676</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ekeberg, Ög</t>
+          <t>Kinda, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523080</v>
+        <v>523191.6660127564</v>
       </c>
       <c r="R25" t="n">
-        <v>6435750</v>
+        <v>6435709.402463616</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3328,45 +3319,49 @@
           <t>2022-12-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Staffan Carlsson</t>
+          <t>Staffan Carlsson, Marika Sjödin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104882696</v>
+        <v>104882700</v>
       </c>
       <c r="B26" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,34 +3369,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2668</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523066.2714913566</v>
+        <v>523080</v>
       </c>
       <c r="R26" t="n">
-        <v>6435577.460562987</v>
+        <v>6435750</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3431,27 +3434,18 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3470,58 +3464,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104882650</v>
+        <v>104882696</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
+        <v>93142</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2668</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523146.9117766089</v>
+        <v>523066.2714913566</v>
       </c>
       <c r="R27" t="n">
-        <v>6435839.82272835</v>
+        <v>6435577.460562987</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3572,7 +3558,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3591,7 +3576,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104882647</v>
+        <v>104882650</v>
       </c>
       <c r="B28" t="n">
         <v>96334</v>
@@ -3626,7 +3611,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -3639,10 +3624,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523101.7484556587</v>
+        <v>523146.9117766089</v>
       </c>
       <c r="R28" t="n">
-        <v>6435767.078363764</v>
+        <v>6435839.82272835</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3712,10 +3697,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104882710</v>
+        <v>104882647</v>
       </c>
       <c r="B29" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3724,38 +3709,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>522953.7786113463</v>
+        <v>523101.7484556587</v>
       </c>
       <c r="R29" t="n">
-        <v>6435781.037015788</v>
+        <v>6435767.078363764</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3806,6 +3799,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3824,7 +3818,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104882711</v>
+        <v>104882710</v>
       </c>
       <c r="B30" t="n">
         <v>98520</v>
@@ -3864,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523067.8098159428</v>
+        <v>522953.7786113463</v>
       </c>
       <c r="R30" t="n">
-        <v>6435769.527056469</v>
+        <v>6435781.037015788</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3936,7 +3930,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104882712</v>
+        <v>104882711</v>
       </c>
       <c r="B31" t="n">
         <v>98520</v>
@@ -3976,10 +3970,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523085.238060271</v>
+        <v>523067.8098159428</v>
       </c>
       <c r="R31" t="n">
-        <v>6435506.141688671</v>
+        <v>6435769.527056469</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4048,10 +4042,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104882648</v>
+        <v>104882712</v>
       </c>
       <c r="B32" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4060,46 +4054,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523170.5990209827</v>
+        <v>523085.238060271</v>
       </c>
       <c r="R32" t="n">
-        <v>6435686.000303307</v>
+        <v>6435506.141688671</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4150,7 +4136,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4169,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104882709</v>
+        <v>104882648</v>
       </c>
       <c r="B33" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,38 +4166,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>522931.0717300316</v>
+        <v>523170.5990209827</v>
       </c>
       <c r="R33" t="n">
-        <v>6435766.092263952</v>
+        <v>6435686.000303307</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4263,6 +4256,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4281,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104882651</v>
+        <v>104882709</v>
       </c>
       <c r="B34" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,46 +4287,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523083.2403314993</v>
+        <v>522931.0717300316</v>
       </c>
       <c r="R34" t="n">
-        <v>6435484.965800423</v>
+        <v>6435766.092263952</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4383,7 +4369,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4402,10 +4387,15 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129572938</v>
+        <v>104882651</v>
       </c>
       <c r="B35" t="n">
-        <v>98778</v>
+        <v>96334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4432,27 +4422,26 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>250 m V Trollgölen, 250 m V Trollgölen, Ög</t>
+          <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523100</v>
+        <v>523083.2403314993</v>
       </c>
       <c r="R35" t="n">
-        <v>6435787</v>
+        <v>6435484.965800423</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4476,17 +4465,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ca 75-100 pl.</t>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,28 +4489,29 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin, Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129573058</v>
+        <v>129572938</v>
       </c>
       <c r="B36" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4543,7 +4538,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4557,10 +4552,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523149</v>
+        <v>523100</v>
       </c>
       <c r="R36" t="n">
-        <v>6435788</v>
+        <v>6435787</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4597,7 +4592,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Vid torrtall</t>
+          <t>Ca 75-100 pl.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4624,10 +4619,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129573170</v>
+        <v>129573058</v>
       </c>
       <c r="B37" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4668,10 +4663,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523121</v>
+        <v>523149</v>
       </c>
       <c r="R37" t="n">
-        <v>6435818</v>
+        <v>6435788</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4708,7 +4703,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Vid stora aspen.</t>
+          <t>Vid torrtall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4735,48 +4730,57 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129582787</v>
+        <v>129573170</v>
       </c>
       <c r="B38" t="n">
-        <v>97024</v>
+        <v>98780</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>250 m V Trollgölen, 250 m V Trollgölen, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523084</v>
+        <v>523121</v>
       </c>
       <c r="R38" t="n">
-        <v>6435828</v>
+        <v>6435818</v>
       </c>
       <c r="S38" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4806,6 +4810,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Vid stora aspen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4829,6 +4838,103 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129582787</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97026</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>53</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>250 m V Trollgölen, 250 m V Trollgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>523084</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6435828</v>
+      </c>
+      <c r="S39" t="n">
+        <v>30</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>129572938</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129573058</v>
       </c>
       <c r="B37" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>129573170</v>
       </c>
       <c r="B38" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>129582787</v>
       </c>
       <c r="B39" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -4511,7 +4511,7 @@
         <v>129572938</v>
       </c>
       <c r="B36" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129573058</v>
       </c>
       <c r="B37" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>129573170</v>
       </c>
       <c r="B38" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>129582787</v>
       </c>
       <c r="B39" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>104882700</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         <v>129572938</v>
       </c>
       <c r="B36" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>129573058</v>
       </c>
       <c r="B37" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>129573170</v>
       </c>
       <c r="B38" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>129582787</v>
       </c>
       <c r="B39" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>98178223</v>
       </c>
       <c r="B24" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>59701663</v>
       </c>
       <c r="B2" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522998.0109878918</v>
+        <v>522998</v>
       </c>
       <c r="R2" t="n">
-        <v>6435740.024460705</v>
+        <v>6435740</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2015-10-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>59701656</v>
+        <v>95578365</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>250 m V Trollgölen, Ög</t>
+          <t>Trollgölen SV, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523132.0152971921</v>
+        <v>522964</v>
       </c>
       <c r="R3" t="n">
-        <v>6435849.259311905</v>
+        <v>6435790</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-10-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,49 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95578350</v>
+        <v>95578367</v>
       </c>
       <c r="B4" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523124.1611120645</v>
+        <v>522954</v>
       </c>
       <c r="R4" t="n">
-        <v>6435741.283787625</v>
+        <v>6435768</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95578367</v>
+        <v>95578215</v>
       </c>
       <c r="B5" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>522953.8517716687</v>
+        <v>523023</v>
       </c>
       <c r="R5" t="n">
-        <v>6435768.339741361</v>
+        <v>6435835</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1034,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95578241</v>
+        <v>95578244</v>
       </c>
       <c r="B6" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523084.6619889531</v>
+        <v>522919</v>
       </c>
       <c r="R6" t="n">
-        <v>6435514.074939375</v>
+        <v>6435754</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1131,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,53 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95578214</v>
+        <v>104882709</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trollgölen SV, Ög</t>
+          <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523065.1932525746</v>
+        <v>522931</v>
       </c>
       <c r="R7" t="n">
-        <v>6435763.692114795</v>
+        <v>6435766</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,65 +1245,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin, Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95578212</v>
+        <v>104882710</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Trollgölen SV, Ög</t>
+          <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523069.6142509431</v>
+        <v>522954</v>
       </c>
       <c r="R8" t="n">
-        <v>6435457.902215949</v>
+        <v>6435781</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin, Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95578365</v>
+        <v>95578325</v>
       </c>
       <c r="B9" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>392</v>
+        <v>230552</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Gropig skägglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Usnea barbata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Weber ex F.H.Wigg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>522963.794667102</v>
+        <v>522977</v>
       </c>
       <c r="R9" t="n">
-        <v>6435790.617985562</v>
+        <v>6435821</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1532,19 +1422,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95578225</v>
+        <v>95578192</v>
       </c>
       <c r="B10" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523096.1350746644</v>
+        <v>523088</v>
       </c>
       <c r="R10" t="n">
-        <v>6435821.010789154</v>
+        <v>6435516</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,19 +1519,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,53 +1548,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95578242</v>
+        <v>129582787</v>
       </c>
       <c r="B11" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trollgölen SV, Ög</t>
+          <t>250 m V Trollgölen, 250 m V Trollgölen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523097.2810514737</v>
+        <v>523084</v>
       </c>
       <c r="R11" t="n">
-        <v>6435806.203591546</v>
+        <v>6435828</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,49 +1633,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jens Johannesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95578342</v>
+        <v>95578345</v>
       </c>
       <c r="B12" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6457</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523120.5796844788</v>
+        <v>523081</v>
       </c>
       <c r="R12" t="n">
-        <v>6435719.041772292</v>
+        <v>6435448</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1868,19 +1713,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95578324</v>
+        <v>95578212</v>
       </c>
       <c r="B13" t="n">
-        <v>77698</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230552</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523132.2501830955</v>
+        <v>523069</v>
       </c>
       <c r="R13" t="n">
-        <v>6435717.522285411</v>
+        <v>6435458</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1980,19 +1810,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95578336</v>
+        <v>95578213</v>
       </c>
       <c r="B14" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523145.6245973038</v>
+        <v>523143</v>
       </c>
       <c r="R14" t="n">
-        <v>6435696.436768513</v>
+        <v>6435631</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2092,19 +1907,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95578213</v>
+        <v>95578214</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523142.2952596105</v>
+        <v>523065</v>
       </c>
       <c r="R15" t="n">
-        <v>6435630.810799366</v>
+        <v>6435763</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2204,19 +2004,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95578235</v>
+        <v>95578350</v>
       </c>
       <c r="B16" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523137.4247864059</v>
+        <v>523124</v>
       </c>
       <c r="R16" t="n">
-        <v>6435739.244497617</v>
+        <v>6435742</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2316,19 +2101,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95578312</v>
+        <v>97662834</v>
       </c>
       <c r="B17" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2371,34 +2141,36 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6439</v>
+        <v>2666</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Trollgölen SV, Ög</t>
+          <t>Kinda, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523049.4018791808</v>
+        <v>523210</v>
       </c>
       <c r="R17" t="n">
-        <v>6435744.554068347</v>
+        <v>6435698</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2425,22 +2197,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,65 +2227,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95578345</v>
+        <v>104882696</v>
       </c>
       <c r="B18" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>2668</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Trubbfjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Homalia trichomanoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Trollgölen SV, Ög</t>
+          <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523080.8044416096</v>
+        <v>523066</v>
       </c>
       <c r="R18" t="n">
-        <v>6435447.913870654</v>
+        <v>6435578</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2537,22 +2304,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,49 +2324,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin, Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95578215</v>
+        <v>95578336</v>
       </c>
       <c r="B19" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2371,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523022.9063465315</v>
+        <v>523146</v>
       </c>
       <c r="R19" t="n">
-        <v>6435834.871625184</v>
+        <v>6435697</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2652,19 +2404,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,37 +2433,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95578323</v>
+        <v>95578315</v>
       </c>
       <c r="B20" t="n">
-        <v>77698</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>230552</v>
+        <v>2779</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropig skägglav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Usnea barbata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2468,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523089.9291147229</v>
+        <v>523204</v>
       </c>
       <c r="R20" t="n">
-        <v>6435519.925616725</v>
+        <v>6435611</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2764,19 +2501,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,53 +2530,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95578192</v>
+        <v>104882697</v>
       </c>
       <c r="B21" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Trollgölen SV, Ög</t>
+          <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523087.8302380443</v>
+        <v>523048</v>
       </c>
       <c r="R21" t="n">
-        <v>6435516.209719121</v>
+        <v>6435552</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2873,22 +2595,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,49 +2615,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Marika Sjödin, Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95578288</v>
+        <v>95578241</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2662,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523139.1240099636</v>
+        <v>523085</v>
       </c>
       <c r="R22" t="n">
-        <v>6435811.737079988</v>
+        <v>6435514</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2988,19 +2695,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,37 +2724,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95578289</v>
+        <v>95578242</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2759,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523088.1721389383</v>
+        <v>523098</v>
       </c>
       <c r="R23" t="n">
-        <v>6435823.080888914</v>
+        <v>6435806</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3100,19 +2792,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,48 +2821,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>98178223</v>
+        <v>95578225</v>
       </c>
       <c r="B24" t="n">
-        <v>98833</v>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Trollgölen, V, Ög</t>
+          <t>Trollgölen SV, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523123</v>
+        <v>523096</v>
       </c>
       <c r="R24" t="n">
-        <v>6435810</v>
+        <v>6435821</v>
       </c>
       <c r="S24" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3200,11 +2882,6 @@
       <c r="W24" t="inlineStr">
         <is>
           <t>Kisa</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>E-Kin-0540</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3229,7 +2906,7 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3237,23 +2914,14 @@
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>104873058</v>
       </c>
       <c r="B25" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,10 +2954,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523191.6660127564</v>
+        <v>523191</v>
       </c>
       <c r="R25" t="n">
-        <v>6435709.402463616</v>
+        <v>6435709</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3358,10 +3026,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104882700</v>
+        <v>95578312</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>83290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,45 +3037,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ekeberg, Ög</t>
+          <t>Trollgölen SV, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523080</v>
+        <v>523049</v>
       </c>
       <c r="R26" t="n">
-        <v>6435750</v>
+        <v>6435744</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3431,12 +3091,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3445,34 +3105,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Staffan Carlsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104882696</v>
+        <v>95578235</v>
       </c>
       <c r="B27" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,37 +3134,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2668</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ekeberg, Ög</t>
+          <t>Trollgölen SV, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523066.2714913566</v>
+        <v>523137</v>
       </c>
       <c r="R27" t="n">
-        <v>6435577.460562987</v>
+        <v>6435739</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3534,22 +3188,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,73 +3208,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Staffan Carlsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104882650</v>
+        <v>95578342</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6457</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ekeberg, Ög</t>
+          <t>Trollgölen SV, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523146.9117766089</v>
+        <v>523120</v>
       </c>
       <c r="R28" t="n">
-        <v>6435839.82272835</v>
+        <v>6435719</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3654,22 +3285,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,66 +3299,60 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Staffan Carlsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104882647</v>
+        <v>104882700</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3745,10 +3360,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523101.7484556587</v>
+        <v>523080</v>
       </c>
       <c r="R29" t="n">
-        <v>6435767.078363764</v>
+        <v>6435750</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3778,19 +3393,9 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3818,53 +3423,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104882710</v>
+        <v>95578288</v>
       </c>
       <c r="B30" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ekeberg, Ög</t>
+          <t>Trollgölen SV, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>522953.7786113463</v>
+        <v>523139</v>
       </c>
       <c r="R30" t="n">
-        <v>6435781.037015788</v>
+        <v>6435811</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3888,22 +3488,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,65 +3508,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Staffan Carlsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104882711</v>
+        <v>95578289</v>
       </c>
       <c r="B31" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekeberg, Ög</t>
+          <t>Trollgölen SV, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523067.8098159428</v>
+        <v>523088</v>
       </c>
       <c r="R31" t="n">
-        <v>6435769.527056469</v>
+        <v>6435823</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4000,22 +3585,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4030,65 +3605,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Staffan Carlsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104882712</v>
+        <v>98178222</v>
       </c>
       <c r="B32" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ekeberg, Ög</t>
+          <t>Trollgölen, V, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523085.238060271</v>
+        <v>523123</v>
       </c>
       <c r="R32" t="n">
-        <v>6435506.141688671</v>
+        <v>6435810</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,24 +3680,19 @@
           <t>Kisa</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>E-Kin-0540</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4142,27 +3707,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marika Sjödin, Staffan Carlsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104882648</v>
+        <v>104882647</v>
       </c>
       <c r="B33" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4189,7 +3753,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4202,10 +3766,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523170.5990209827</v>
+        <v>523102</v>
       </c>
       <c r="R33" t="n">
-        <v>6435686.000303307</v>
+        <v>6435767</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4235,19 +3799,9 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4275,50 +3829,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104882709</v>
+        <v>104882648</v>
       </c>
       <c r="B34" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>522931.0717300316</v>
+        <v>523171</v>
       </c>
       <c r="R34" t="n">
-        <v>6435766.092263952</v>
+        <v>6435686</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4348,27 +3905,18 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4387,15 +3935,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104882651</v>
+        <v>104882650</v>
       </c>
       <c r="B35" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4422,7 +3965,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4435,10 +3978,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523083.2403314993</v>
+        <v>523147</v>
       </c>
       <c r="R35" t="n">
-        <v>6435484.965800423</v>
+        <v>6435840</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4468,19 +4011,9 @@
           <t>2022-12-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2022-12-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,10 +4041,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129572938</v>
+        <v>104882651</v>
       </c>
       <c r="B36" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4538,27 +4071,26 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>250 m V Trollgölen, 250 m V Trollgölen, Ög</t>
+          <t>Ekeberg, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523100</v>
+        <v>523083</v>
       </c>
       <c r="R36" t="n">
-        <v>6435787</v>
+        <v>6435485</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4582,17 +4114,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ca 75-100 pl.</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4601,28 +4128,29 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jens Johannesson</t>
+          <t>Marika Sjödin, Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129573058</v>
+        <v>129572938</v>
       </c>
       <c r="B37" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4649,7 +4177,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4663,10 +4191,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523149</v>
+        <v>523100</v>
       </c>
       <c r="R37" t="n">
-        <v>6435788</v>
+        <v>6435787</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4703,7 +4231,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Vid torrtall</t>
+          <t>Ca 75-100 pl.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4730,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129573170</v>
+        <v>129573058</v>
       </c>
       <c r="B38" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4774,10 +4302,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523121</v>
+        <v>523149</v>
       </c>
       <c r="R38" t="n">
-        <v>6435818</v>
+        <v>6435788</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4814,7 +4342,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Vid stora aspen.</t>
+          <t>Vid torrtall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,48 +4369,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129582787</v>
+        <v>129573170</v>
       </c>
       <c r="B39" t="n">
-        <v>97043</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>250 m V Trollgölen, 250 m V Trollgölen, Ög</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523084</v>
+        <v>523121</v>
       </c>
       <c r="R39" t="n">
-        <v>6435828</v>
+        <v>6435818</v>
       </c>
       <c r="S39" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4912,6 +4449,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Vid stora aspen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4935,6 +4477,588 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>59701656</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>250 m V Trollgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>523132</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6435849</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2015-10-21</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2015-10-21</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>104882711</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ekeberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>523068</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6435770</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>104882712</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ekeberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>523085</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6435506</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>104882713</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ekeberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>523048</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6435552</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-12-01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>95578323</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Trollgölen SV, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>523090</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6435520</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>95578324</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79515</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>230552</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Gropig skägglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Usnea barbata</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Trollgölen SV, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>523132</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6435717</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51780-2022 artfynd.xlsx
+++ b/artfynd/A 51780-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578192</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129582787</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578345</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59701663</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578365</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578367</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578212</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578213</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578214</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578215</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578350</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97662834</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882696</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578336</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,6 +2214,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578315</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882697</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578241</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578242</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578244</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578225</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2732,6 +2837,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104873058</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2829,6 +2939,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578312</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2926,6 +3041,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578235</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3023,6 +3143,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578342</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3129,6 +3254,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882700</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3226,6 +3356,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578288</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3323,6 +3458,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578289</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3427,6 +3567,11 @@
       <c r="AY29" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98178222</t>
         </is>
       </c>
     </row>
@@ -3535,6 +3680,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882647</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3641,6 +3791,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882648</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3747,6 +3902,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882650</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3853,6 +4013,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882651</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3964,6 +4129,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129572938</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4075,6 +4245,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129573058</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4186,6 +4361,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129573170</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4283,6 +4463,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59701656</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4380,6 +4565,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882709</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4477,6 +4667,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882710</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4574,6 +4769,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882711</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4671,6 +4871,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882712</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4768,6 +4973,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104882713</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4865,6 +5075,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578323</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4962,6 +5177,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578324</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5059,8 +5279,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95578325</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>